--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/1326-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/1326-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A5FA0CEA-791C-406F-A614-75C554BA32E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8B42A6BD-9424-43F1-8816-A7B36282C667}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{4864C56F-9C9F-4167-8D7A-15EB9FEC9426}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{5FAFB0D4-0EB7-48C3-B5E2-529F1107BDD2}"/>
   </bookViews>
   <sheets>
     <sheet name="1326-dividend-20260215_1_2" sheetId="2" r:id="rId1"/>
@@ -1613,29 +1613,28 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E55D16C-1A17-4297-AF9A-E4F7D15ED478}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03259DAC-3F6F-4CEE-A45D-FE454FFDAA1A}">
   <dimension ref="A1:X57"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="10.75" customWidth="1"/>
-    <col min="3" max="3" width="9.75" customWidth="1"/>
-    <col min="4" max="4" width="6.25" customWidth="1"/>
-    <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="7" width="6.25" customWidth="1"/>
-    <col min="8" max="8" width="6" customWidth="1"/>
-    <col min="9" max="10" width="6.25" customWidth="1"/>
-    <col min="11" max="13" width="6" customWidth="1"/>
-    <col min="14" max="15" width="6.25" customWidth="1"/>
-    <col min="16" max="18" width="6" customWidth="1"/>
-    <col min="19" max="19" width="6.25" customWidth="1"/>
-    <col min="20" max="20" width="6" customWidth="1"/>
-    <col min="21" max="21" width="6.25" customWidth="1"/>
-    <col min="22" max="22" width="6" customWidth="1"/>
-    <col min="23" max="23" width="6.25" customWidth="1"/>
-    <col min="24" max="24" width="6.875" customWidth="1"/>
+    <col min="3" max="3" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="5.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
@@ -1669,7 +1668,7 @@
       <c r="W1" s="31"/>
       <c r="X1" s="23"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="24" t="s">
         <v>1</v>
       </c>
@@ -1705,7 +1704,7 @@
       <c r="W2" s="33"/>
       <c r="X2" s="34"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="24" t="s">
         <v>2</v>
       </c>
@@ -1757,7 +1756,7 @@
       </c>
       <c r="X3" s="37"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="26"/>
       <c r="B4" s="27"/>
       <c r="C4" s="7"/>
@@ -1825,7 +1824,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="38">
         <v>2024</v>
       </c>
@@ -1897,7 +1896,7 @@
         <v>2.2999999999999998</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="40">
         <v>2023</v>
       </c>
@@ -1969,7 +1968,7 @@
         <v>4.5999999999999996</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="38">
         <v>2022</v>
       </c>
@@ -2041,7 +2040,7 @@
         <v>1.59</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="40">
         <v>2021</v>
       </c>
@@ -2113,7 +2112,7 @@
         <v>7.47</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="38">
         <v>2020</v>
       </c>
@@ -2185,7 +2184,7 @@
         <v>3.23</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="40">
         <v>2019</v>
       </c>
@@ -2257,7 +2256,7 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="38">
         <v>2018</v>
       </c>
@@ -2329,7 +2328,7 @@
         <v>7.29</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="40">
         <v>2017</v>
       </c>
@@ -2401,7 +2400,7 @@
         <v>7.03</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="38">
         <v>2016</v>
       </c>
@@ -2473,7 +2472,7 @@
         <v>6.36</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="40">
         <v>2015</v>
       </c>
@@ -2545,7 +2544,7 @@
         <v>5.25</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="38">
         <v>2014</v>
       </c>
@@ -2617,7 +2616,7 @@
         <v>2.0299999999999998</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="40">
         <v>2013</v>
       </c>
@@ -2689,7 +2688,7 @@
         <v>4.05</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="38">
         <v>2012</v>
       </c>
@@ -2761,7 +2760,7 @@
         <v>1.44</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="40">
         <v>2011</v>
       </c>
@@ -2833,7 +2832,7 @@
         <v>6.81</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="38">
         <v>2010</v>
       </c>
@@ -2905,7 +2904,7 @@
         <v>10.199999999999999</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="40">
         <v>2009</v>
       </c>
@@ -2977,7 +2976,7 @@
         <v>6.79</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="38">
         <v>2008</v>
       </c>
@@ -3049,7 +3048,7 @@
         <v>3.6</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="40">
         <v>2007</v>
       </c>
@@ -3121,7 +3120,7 @@
         <v>17.7</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="38">
         <v>2006</v>
       </c>
@@ -3193,7 +3192,7 @@
         <v>8.9700000000000006</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="40">
         <v>2005</v>
       </c>
@@ -3265,7 +3264,7 @@
         <v>12.6</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="38">
         <v>2004</v>
       </c>
@@ -3337,7 +3336,7 @@
         <v>11.3</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="40">
         <v>2003</v>
       </c>
@@ -3409,7 +3408,7 @@
         <v>7.44</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="42">
         <v>2002</v>
       </c>
@@ -3481,7 +3480,7 @@
         <v>7.82</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="44"/>
       <c r="B28" s="45"/>
       <c r="C28" s="19" t="s">
@@ -3509,7 +3508,7 @@
       <c r="W28" s="51"/>
       <c r="X28" s="47"/>
     </row>
-    <row r="29" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="52">
         <v>2001</v>
       </c>
@@ -3581,7 +3580,7 @@
         <v>5.1100000000000003</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="54"/>
       <c r="B30" s="55"/>
       <c r="C30" s="21" t="s">
@@ -3609,7 +3608,7 @@
       <c r="W30" s="61"/>
       <c r="X30" s="57"/>
     </row>
-    <row r="31" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="42">
         <v>2000</v>
       </c>
@@ -3681,7 +3680,7 @@
         <v>9.14</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="44"/>
       <c r="B32" s="45"/>
       <c r="C32" s="19" t="s">
@@ -3709,7 +3708,7 @@
       <c r="W32" s="51"/>
       <c r="X32" s="47"/>
     </row>
-    <row r="33" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="52">
         <v>1999</v>
       </c>
@@ -3781,7 +3780,7 @@
         <v>6.67</v>
       </c>
     </row>
-    <row r="34" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="54"/>
       <c r="B34" s="55"/>
       <c r="C34" s="21" t="s">
@@ -3809,7 +3808,7 @@
       <c r="W34" s="61"/>
       <c r="X34" s="57"/>
     </row>
-    <row r="35" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="42">
         <v>1998</v>
       </c>
@@ -3881,7 +3880,7 @@
         <v>3.45</v>
       </c>
     </row>
-    <row r="36" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A36" s="44"/>
       <c r="B36" s="45"/>
       <c r="C36" s="19" t="s">
@@ -3909,7 +3908,7 @@
       <c r="W36" s="51"/>
       <c r="X36" s="47"/>
     </row>
-    <row r="37" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A37" s="40">
         <v>1997</v>
       </c>
@@ -3981,7 +3980,7 @@
         <v>3.14</v>
       </c>
     </row>
-    <row r="38" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A38" s="42">
         <v>1996</v>
       </c>
@@ -4053,7 +4052,7 @@
         <v>2.64</v>
       </c>
     </row>
-    <row r="39" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A39" s="44"/>
       <c r="B39" s="45"/>
       <c r="C39" s="19" t="s">
@@ -4081,7 +4080,7 @@
       <c r="W39" s="51"/>
       <c r="X39" s="47"/>
     </row>
-    <row r="40" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A40" s="40">
         <v>1995</v>
       </c>
@@ -4153,7 +4152,7 @@
         <v>5.94</v>
       </c>
     </row>
-    <row r="41" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A41" s="38">
         <v>1994</v>
       </c>
@@ -4225,7 +4224,7 @@
         <v>5.99</v>
       </c>
     </row>
-    <row r="42" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A42" s="40">
         <v>1993</v>
       </c>
@@ -4297,7 +4296,7 @@
         <v>3.98</v>
       </c>
     </row>
-    <row r="43" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A43" s="42">
         <v>1992</v>
       </c>
@@ -4369,7 +4368,7 @@
         <v>6.6</v>
       </c>
     </row>
-    <row r="44" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A44" s="44"/>
       <c r="B44" s="45"/>
       <c r="C44" s="19" t="s">
@@ -4397,7 +4396,7 @@
       <c r="W44" s="51"/>
       <c r="X44" s="47"/>
     </row>
-    <row r="45" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A45" s="52">
         <v>1991</v>
       </c>
@@ -4469,7 +4468,7 @@
         <v>9.09</v>
       </c>
     </row>
-    <row r="46" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A46" s="54"/>
       <c r="B46" s="55"/>
       <c r="C46" s="21" t="s">
@@ -4497,7 +4496,7 @@
       <c r="W46" s="61"/>
       <c r="X46" s="57"/>
     </row>
-    <row r="47" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A47" s="42">
         <v>1990</v>
       </c>
@@ -4569,7 +4568,7 @@
         <v>6.94</v>
       </c>
     </row>
-    <row r="48" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A48" s="44"/>
       <c r="B48" s="45"/>
       <c r="C48" s="19" t="s">
@@ -4597,7 +4596,7 @@
       <c r="W48" s="51"/>
       <c r="X48" s="47"/>
     </row>
-    <row r="49" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A49" s="52">
         <v>1989</v>
       </c>
@@ -4669,7 +4668,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="50" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A50" s="54"/>
       <c r="B50" s="55"/>
       <c r="C50" s="21" t="s">
@@ -4697,7 +4696,7 @@
       <c r="W50" s="61"/>
       <c r="X50" s="57"/>
     </row>
-    <row r="51" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A51" s="38">
         <v>1988</v>
       </c>
@@ -4769,7 +4768,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="52" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A52" s="40">
         <v>1987</v>
       </c>
@@ -4841,7 +4840,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="53" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A53" s="38">
         <v>1986</v>
       </c>
@@ -4913,7 +4912,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="54" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A54" s="40">
         <v>1985</v>
       </c>
@@ -4985,7 +4984,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="55" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A55" s="38">
         <v>1984</v>
       </c>
@@ -5057,7 +5056,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="56" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A56" s="40">
         <v>1983</v>
       </c>
@@ -5129,7 +5128,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="57" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A57" s="38" t="s">
         <v>72</v>
       </c>
